--- a/Assessment Questions/CDA/ADA-134/DECISION MODELING/. Comparing Decisions in Uncertain Settings/. Comparing Decisions in Uncertain Settings.xlsx
+++ b/Assessment Questions/CDA/ADA-134/DECISION MODELING/. Comparing Decisions in Uncertain Settings/. Comparing Decisions in Uncertain Settings.xlsx
@@ -1,132 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manfo\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{288ACAA2-1B41-4401-A0B9-5205F319619E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C320FB9B-291F-404C-8F09-27420E150D50}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>Section,Type,Q.No,Scenario,Question,Option A,Option B,Option C,Option D,Correct Answer</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,1,,Decision under uncertainty uses:,Single outcome,Multiple outcomes,Sorting,None,B</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,2,,Maximax criterion:,Max profit,Min profit,Average,None,A</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,3,,Maximin criterion:,Max of minimum payoffs,Min of max,None,None,A</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,4,,Minimax regret minimizes:,Profit,Regret,Cost,None,B</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,5,,Expected value method uses:,Probability,Sorting,None,None,A</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,6,,Best decision depends on:,Criteria,Sorting,None,None,A</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,7,,Regret means:,Loss from best option,Profit,None,None,A</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,8,Manager chooses highest profit.,Criterion?,Maximax,Maximin,None,None,A</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,9,Manager avoids worst loss.,Criterion?,Maximin,Maximax,None,None,A</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,10,Manager minimizes regret.,Criterion?,Minimax regret,Maximax,None,None,A</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,11,Uses probabilities.,Criterion?,Expected value,Maximax,None,None,A</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,12,Multiple options compared.,Purpose?,Decision making,Sorting,None,None,A</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,Option,,State1,State2,State3,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,A,,1000,2000,3000,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,B,,1500,1800,2500,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,C,,1200,2200,2700,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,13,,Apply Maximax.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,14,,Apply Maximin.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,15,,Calculate regret table.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,16,,Apply Minimax regret.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,17,,Calculate expected value.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,18,,Best decision.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,19,,Compare methods.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,20,,Final recommendation.,,,,,</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -145,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -459,136 +419,762 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE971E7-B65F-4AD6-A8D7-056928ED734E}">
-  <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Decision under uncertainty uses:</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Single outcome</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Multiple outcomes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sorting</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Maximax criterion:</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Max profit</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Min profit</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Maximin criterion:</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Max of minimum payoffs</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Min of max</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Minimax regret minimizes:</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Regret</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Expected value method uses:</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sorting</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Best decision depends on:</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Criteria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sorting</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Regret means:</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Loss from best option</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Criterion?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | Manager chooses highest profit.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Maximax</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Maximin</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Criterion?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | Manager avoids worst loss.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Maximin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Maximax</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Criterion?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | Manager minimizes regret.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Minimax regret</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Maximax</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Criterion?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | Uses probabilities.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Expected value</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Maximax</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Purpose?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | Multiple options compared.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Decision making</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sorting</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset,Dataset,Option,,State1,State2,State3,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset,Dataset,A,,1000,2000,3000,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset,Dataset,B,,1500,1800,2500,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset,Dataset,C,,1200,2200,2700,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Apply Maximax.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Apply Maximin.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>24</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>. Comparing Decisions in Uncertain Settings</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Calculate regret table.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>